--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.47656999200621</v>
+        <v>1.864942623701009</v>
       </c>
       <c r="D2" t="n">
-        <v>9.262318351499053</v>
+        <v>1.505126732118596</v>
       </c>
       <c r="E2" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F2" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.43459806008983</v>
+        <v>5.595622184764597</v>
       </c>
       <c r="D3" t="n">
-        <v>39.10855862525029</v>
+        <v>6.355140776603172</v>
       </c>
       <c r="E3" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F3" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.08036516902058</v>
+        <v>2.125559339965845</v>
       </c>
       <c r="D4" t="n">
-        <v>12.77000505686382</v>
+        <v>2.075125821740371</v>
       </c>
       <c r="E4" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F4" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.31530713240053</v>
+        <v>6.388737409015086</v>
       </c>
       <c r="D5" t="n">
-        <v>23.08679276123039</v>
+        <v>3.751603823699939</v>
       </c>
       <c r="E5" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F5" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.03687334633797</v>
+        <v>3.41849191877992</v>
       </c>
       <c r="D6" t="n">
-        <v>8.634958019585271</v>
+        <v>1.403180678182607</v>
       </c>
       <c r="E6" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F6" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.14054661867315</v>
+        <v>7.010338825534387</v>
       </c>
       <c r="D7" t="n">
-        <v>20.68983171418632</v>
+        <v>3.362097653555277</v>
       </c>
       <c r="E7" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F7" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>47.41048115722036</v>
+        <v>7.704203188048309</v>
       </c>
       <c r="D8" t="n">
-        <v>33.41126307100646</v>
+        <v>5.42933024903855</v>
       </c>
       <c r="E8" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F8" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.20958409559818</v>
+        <v>3.934057415534705</v>
       </c>
       <c r="D9" t="n">
-        <v>8.498843072548128</v>
+        <v>1.381061999289071</v>
       </c>
       <c r="E9" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F9" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>43.17929151445585</v>
+        <v>7.016634871099076</v>
       </c>
       <c r="D10" t="n">
-        <v>43.76320918307661</v>
+        <v>7.11152149224995</v>
       </c>
       <c r="E10" t="n">
-        <v>12.88106553967398</v>
+        <v>2.093173150197022</v>
       </c>
       <c r="F10" t="n">
-        <v>12.94275693614386</v>
+        <v>2.103198002123377</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
